--- a/artfynd/A 24632-2026 artfynd.xlsx
+++ b/artfynd/A 24632-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>134179279</v>
       </c>
       <c r="B3" t="n">
-        <v>96615</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24632-2026 artfynd.xlsx
+++ b/artfynd/A 24632-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113357966</v>
+        <v>134179279</v>
       </c>
       <c r="B2" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Törnsfalls hällmarker, Sm</t>
+          <t>A 24632, Törnfall, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587818</v>
+        <v>587660</v>
       </c>
       <c r="R2" t="n">
-        <v>6407671</v>
+        <v>6407816</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,28 +766,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Emilia Lönegren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134179279</v>
+        <v>113358009</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,49 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 24632, Törnfall, Sm</t>
+          <t>Törnsfalls hällmarker, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587660</v>
+        <v>587832</v>
       </c>
       <c r="R3" t="n">
-        <v>6407816</v>
+        <v>6407727</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,51 +864,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Emilia Lönegren</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134179553</v>
+        <v>134179290</v>
       </c>
       <c r="B4" t="n">
-        <v>58260</v>
+        <v>92188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>3008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -920,13 +915,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587787</v>
+        <v>587660</v>
       </c>
       <c r="R4" t="n">
-        <v>6407639</v>
+        <v>6407816</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,10 +984,325 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Emilia Lönegren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113357966</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Törnsfalls hällmarker, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587818</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6407671</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134179379</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Törnsfall, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587609</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6407741</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Emilia Lönegren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134179553</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 24632, Törnfall, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587787</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6407639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
